--- a/data/trans_orig/IP25B02_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP25B02_2023-Edad-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>433</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>420</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>9817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>9328</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16033</t>
+          <t>15491</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38550</t>
+          <t>38496</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46608</t>
+          <t>46724</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43153</t>
+          <t>42862</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52105</t>
+          <t>52351</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84214</t>
+          <t>84768</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96770</t>
+          <t>96476</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14018</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>12358</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27910</t>
+          <t>27004</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19235</t>
+          <t>19815</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37189</t>
+          <t>36770</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19583</t>
+          <t>20375</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37076</t>
+          <t>35894</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>28600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48292</t>
+          <t>48365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55232</t>
+          <t>55108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79557</t>
+          <t>82600</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40875</t>
+          <t>41446</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61998</t>
+          <t>60264</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48785</t>
+          <t>47926</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70470</t>
+          <t>69115</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>95344</t>
+          <t>95012</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124720</t>
+          <t>124348</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,97%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56618</t>
+          <t>57104</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77283</t>
+          <t>76686</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56024</t>
+          <t>54940</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>78674</t>
+          <t>77460</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>119205</t>
+          <t>118556</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>148685</t>
+          <t>149497</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17658</t>
+          <t>16961</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33141</t>
+          <t>34381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23526</t>
+          <t>23571</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43667</t>
+          <t>43255</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46677</t>
+          <t>45917</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72261</t>
+          <t>71528</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43202</t>
+          <t>41939</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65349</t>
+          <t>65841</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52029</t>
+          <t>51097</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78149</t>
+          <t>77617</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>101505</t>
+          <t>101577</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>135150</t>
+          <t>137502</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46273</t>
+          <t>45293</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68695</t>
+          <t>68145</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61282</t>
+          <t>61745</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88741</t>
+          <t>88910</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114141</t>
+          <t>113695</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>149442</t>
+          <t>150585</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>39,06%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29712</t>
+          <t>29329</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48990</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30872</t>
+          <t>31150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52648</t>
+          <t>52896</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65164</t>
+          <t>63916</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>92821</t>
+          <t>92598</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55105</t>
+          <t>53455</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>138290</t>
+          <t>139770</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76397</t>
+          <t>76967</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>122927</t>
+          <t>126988</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>141496</t>
+          <t>144697</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>241379</t>
+          <t>237516</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58139</t>
+          <t>55879</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95844</t>
+          <t>97933</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74746</t>
+          <t>76917</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108331</t>
+          <t>109781</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>146021</t>
+          <t>141103</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>199734</t>
+          <t>196058</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43584</t>
+          <t>45026</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>78006</t>
+          <t>78663</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64790</t>
+          <t>64567</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>99837</t>
+          <t>97107</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>117599</t>
+          <t>121127</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>167587</t>
+          <t>167728</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>31913</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64964</t>
+          <t>66060</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21803</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41377</t>
+          <t>42508</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60264</t>
+          <t>60767</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>101245</t>
+          <t>96675</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>85106</t>
+          <t>86264</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>187396</t>
+          <t>218937</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>126639</t>
+          <t>124530</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>185511</t>
+          <t>188601</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>225799</t>
+          <t>228551</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>341460</t>
+          <t>359144</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>139227</t>
+          <t>139243</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>189588</t>
+          <t>186463</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>174359</t>
+          <t>175655</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>223244</t>
+          <t>221746</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>331008</t>
+          <t>328278</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>395008</t>
+          <t>398350</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>150845</t>
+          <t>150418</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>198535</t>
+          <t>198701</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>193036</t>
+          <t>194750</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>241405</t>
+          <t>242104</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,47 +3282,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>25,86%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>32,15%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>393865</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>359621</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>426414</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>28,08%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>25,64%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>32,06%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>393865</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>357658</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>430058</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>28,08%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>25,5%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>167760</t>
+          <t>169819</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>219397</t>
+          <t>218479</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>162605</t>
+          <t>165842</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>204902</t>
+          <t>207439</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>345622</t>
+          <t>344280</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>414485</t>
+          <t>411655</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25B02_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP25B02_2023-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de horas al día que emplean en utilizar aparatos electrónicos en fines de semana / solo 2023 en 2023 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según el número de horas al día que utilizan aparatos electrónicos en fin de semana en 2023 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3973</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,31%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>785</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>782</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3838</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3961</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2432</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6871</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>745</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2760</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5531</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,77%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5928</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11,49%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>455</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9817</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3556</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1584</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7456</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>15,59%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2888</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9328</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10,95%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,09%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>9668</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10094</t>
+          <t>9300</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>40108</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36100</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>43097</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>83,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>75,48%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>90,1%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>43102</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>38496</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>46724</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>83,57%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>74,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>90,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48225</t>
+          <t>38116</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42862</t>
+          <t>33828</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52351</t>
+          <t>41848</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>91327</t>
+          <t>78224</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84768</t>
+          <t>72555</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96476</t>
+          <t>83438</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>47830</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47830</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>47830</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>51573</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>51573</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>51573</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>58376</t>
+          <t>46685</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58376</t>
+          <t>46685</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58376</t>
+          <t>46685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>109949</t>
+          <t>94514</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109949</t>
+          <t>94514</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109949</t>
+          <t>94514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17003</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>11207</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>24309</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>10,82%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7,13%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>15,47%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>8561</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5167</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>13895</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19090</t>
+          <t>8503</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12358</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27004</t>
+          <t>14268</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>27651</t>
+          <t>25507</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19815</t>
+          <t>18172</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36770</t>
+          <t>33640</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>33850</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26447</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44165</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16,84%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>28,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>28068</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20375</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35894</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,2%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38252</t>
+          <t>25830</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28600</t>
+          <t>18801</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48365</t>
+          <t>33286</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>66319</t>
+          <t>59679</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55108</t>
+          <t>49410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82600</t>
+          <t>70872</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>50750</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>42164</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>60648</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32,31%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26,84%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>38,61%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>50576</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>41446</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>60264</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>32,79%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>26,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39,07%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58217</t>
+          <t>45964</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47926</t>
+          <t>38476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>55002</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>108793</t>
+          <t>96714</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>95012</t>
+          <t>84036</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124348</t>
+          <t>110298</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55488</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>46994</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>65533</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>35,32%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>29,92%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>41,72%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>67051</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>57104</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>76686</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>43,47%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>37,02%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>49,71%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>66501</t>
+          <t>60655</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54940</t>
+          <t>52052</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>77460</t>
+          <t>69999</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>133552</t>
+          <t>116143</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>118556</t>
+          <t>103719</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>149497</t>
+          <t>128780</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>157091</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>157091</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>157091</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>154256</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>154256</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>154256</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>182060</t>
+          <t>140952</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>182060</t>
+          <t>140952</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182060</t>
+          <t>140952</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>336315</t>
+          <t>298043</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>336315</t>
+          <t>298043</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>336315</t>
+          <t>298043</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>31462</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23108</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>42249</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>21,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>25023</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16961</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>34381</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>14,46%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,8%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>19,87%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32579</t>
+          <t>25848</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23571</t>
+          <t>17761</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43255</t>
+          <t>33906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>57603</t>
+          <t>57310</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45917</t>
+          <t>46660</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71528</t>
+          <t>72022</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -1971,107 +1971,107 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>59687</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>48852</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>72096</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>29,82%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>24,41%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>36,03%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>53655</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>41939</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>65841</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>31,0%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>24,23%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>38,04%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64468</t>
+          <t>54011</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51097</t>
+          <t>44665</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>77617</t>
+          <t>64887</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
+          <t>30,92%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>25,57%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>37,15%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>113699</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>96472</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>130411</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
           <t>30,34%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>24,05%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>36,53%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>118123</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>101577</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>137502</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>30,64%</t>
-        </is>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>70675</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>59393</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>83697</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>35,32%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,68%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>41,82%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>56333</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>45293</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>68145</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>32,55%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>39,37%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>74957</t>
+          <t>55920</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61745</t>
+          <t>45702</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88910</t>
+          <t>66176</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>131291</t>
+          <t>126595</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113695</t>
+          <t>109397</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150585</t>
+          <t>142813</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,1%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>38302</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>28893</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>50538</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>19,14%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>14,44%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>25,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>38061</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>29329</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>47352</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>21,99%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>16,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>27,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>40486</t>
+          <t>38893</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31150</t>
+          <t>30696</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52896</t>
+          <t>48656</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>78547</t>
+          <t>77195</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63916</t>
+          <t>64779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>92598</t>
+          <t>91188</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>88457</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>71827</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>110474</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>30,82%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>25,02%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>38,49%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>79646</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>53455</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>139770</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>29,44%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>51,67%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>97527</t>
+          <t>57330</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76967</t>
+          <t>45359</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>126988</t>
+          <t>71059</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>177173</t>
+          <t>145788</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>144697</t>
+          <t>125311</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>237516</t>
+          <t>175686</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>91498</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>76088</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>107865</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>31,88%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>26,51%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>37,58%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>80648</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>55879</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>97933</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>29,81%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>20,66%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>36,2%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>91955</t>
+          <t>83589</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76917</t>
+          <t>71474</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>109781</t>
+          <t>97361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>172603</t>
+          <t>175088</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>141103</t>
+          <t>155769</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>196058</t>
+          <t>196818</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>80284</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>64892</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>96444</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>22,61%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>33,6%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>63692</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>45026</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>78663</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>16,64%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>29,08%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>79995</t>
+          <t>67977</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64567</t>
+          <t>55566</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>97107</t>
+          <t>82099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>143688</t>
+          <t>148261</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>121127</t>
+          <t>128446</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>167728</t>
+          <t>169055</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>31,4%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>26815</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>19476</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>35355</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>9,34%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>6,78%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>12,32%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>46542</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>31913</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>66060</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>17,2%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>11,8%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>24,42%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>30606</t>
+          <t>42450</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21912</t>
+          <t>32951</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42508</t>
+          <t>53906</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>77149</t>
+          <t>69265</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60767</t>
+          <t>56079</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96675</t>
+          <t>84811</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>287054</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>287054</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>287054</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>336</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>270529</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>270529</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>270529</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>300084</t>
+          <t>251347</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>300084</t>
+          <t>251347</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>300084</t>
+          <t>251347</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>570612</t>
+          <t>538402</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>570612</t>
+          <t>538402</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>570612</t>
+          <t>538402</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,72 +2996,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>138329</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>116632</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>167913</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>19,99%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>16,85%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>24,26%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>114015</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>86264</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>218937</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>17,56%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>13,28%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>33,71%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>151628</t>
+          <t>92464</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>124530</t>
+          <t>77079</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>188601</t>
+          <t>109104</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>265643</t>
+          <t>230793</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>228551</t>
+          <t>204123</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>359144</t>
+          <t>264423</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>187796</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>166155</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>210546</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>27,13%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>24,01%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>30,42%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>164409</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>139243</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>186463</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>25,32%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>21,44%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>28,71%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>197947</t>
+          <t>165472</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>175655</t>
+          <t>147236</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>221746</t>
+          <t>185905</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>362356</t>
+          <t>353268</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>328278</t>
+          <t>325779</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>398350</t>
+          <t>382807</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -3222,72 +3222,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>205265</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>183932</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>230498</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>29,66%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>26,58%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>176249</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>150418</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>198701</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>27,14%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>23,16%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>30,6%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>217616</t>
+          <t>175606</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>194750</t>
+          <t>158952</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>242104</t>
+          <t>195763</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>393865</t>
+          <t>380870</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>359621</t>
+          <t>353107</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>426414</t>
+          <t>412017</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -3335,72 +3335,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>160712</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>143086</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>179366</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>23,22%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>20,67%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>25,92%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>194756</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>169819</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>218479</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>29,99%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>26,15%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>33,64%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>185818</t>
+          <t>180114</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>165842</t>
+          <t>163510</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>207439</t>
+          <t>200514</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>380574</t>
+          <t>340826</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>344280</t>
+          <t>314655</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>411655</t>
+          <t>369055</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>692101</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>692101</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>692101</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>917</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>649430</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>649430</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>649430</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>753009</t>
+          <t>613656</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>753009</t>
+          <t>613656</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>753009</t>
+          <t>613656</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1402439</t>
+          <t>1305757</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1402439</t>
+          <t>1305757</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1402439</t>
+          <t>1305757</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
